--- a/checklist_&_test_case_&_bug_report/testing_papa_pizza.xlsx
+++ b/checklist_&_test_case_&_bug_report/testing_papa_pizza.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zohir\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF8DAD1E-D1D6-4EF0-A1A0-83AD97ED6100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{591EF140-451D-4E27-95F2-0DD646837DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="1950" windowWidth="24240" windowHeight="13140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="125">
   <si>
     <t>Номер</t>
   </si>
@@ -346,9 +346,6 @@
   </si>
   <si>
     <t>Низкий</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	Средний</t>
   </si>
   <si>
     <t>Увеличение количества товара</t>
@@ -1026,7 +1023,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="155">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1112,46 +1109,213 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1160,199 +1324,79 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1379,83 +1423,39 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Гиперссылка" xfId="3" builtinId="8"/>
@@ -1846,8 +1846,8 @@
       <c r="A9" s="30">
         <v>8</v>
       </c>
-      <c r="B9" s="147" t="s">
-        <v>105</v>
+      <c r="B9" s="39" t="s">
+        <v>104</v>
       </c>
       <c r="C9" s="11"/>
     </row>
@@ -1919,13 +1919,13 @@
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="148" t="s">
-        <v>106</v>
-      </c>
-      <c r="C1" s="90"/>
-      <c r="D1" s="90"/>
-      <c r="E1" s="90"/>
-      <c r="F1" s="91"/>
+      <c r="B1" s="69" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="71"/>
     </row>
     <row r="2" spans="1:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -1948,1026 +1948,964 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="46">
+      <c r="A3" s="50">
         <v>1</v>
       </c>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="72" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="149" t="s">
-        <v>107</v>
-      </c>
-      <c r="E3" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="F3" s="82" t="s">
+      <c r="D3" s="65" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" s="153" t="s">
+        <v>103</v>
+      </c>
+      <c r="F3" s="75" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="47"/>
-      <c r="B4" s="92"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="73"/>
       <c r="C4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="92"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="58"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="154"/>
+      <c r="F4" s="62"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="47"/>
-      <c r="B5" s="92"/>
-      <c r="C5" s="150" t="s">
+      <c r="A5" s="51"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="73"/>
+      <c r="E5" s="154"/>
+      <c r="F5" s="62"/>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="52"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="41" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="92"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="58"/>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="48"/>
-      <c r="B6" s="93"/>
-      <c r="C6" s="151" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" s="93"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="59"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="155"/>
+      <c r="F6" s="63"/>
     </row>
     <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="89"/>
-      <c r="B7" s="89"/>
-      <c r="C7" s="89"/>
-      <c r="D7" s="89"/>
-      <c r="E7" s="89"/>
-      <c r="F7" s="89"/>
+      <c r="A7" s="76"/>
+      <c r="B7" s="76"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="76"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="76"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="60">
+      <c r="A8" s="81">
         <v>2</v>
       </c>
-      <c r="B8" s="66" t="s">
+      <c r="B8" s="84" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="152" t="s">
-        <v>110</v>
-      </c>
-      <c r="E8" s="83" t="s">
+      <c r="D8" s="87" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" s="88" t="s">
         <v>100</v>
       </c>
-      <c r="F8" s="86" t="s">
+      <c r="F8" s="91" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="61"/>
-      <c r="B9" s="67"/>
+      <c r="A9" s="82"/>
+      <c r="B9" s="85"/>
       <c r="C9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="67"/>
-      <c r="E9" s="84"/>
-      <c r="F9" s="87"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="89"/>
+      <c r="F9" s="92"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="61"/>
-      <c r="B10" s="67"/>
+      <c r="A10" s="82"/>
+      <c r="B10" s="85"/>
       <c r="C10" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="D10" s="67"/>
-      <c r="E10" s="84"/>
-      <c r="F10" s="87"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="89"/>
+      <c r="F10" s="92"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="61"/>
-      <c r="B11" s="67"/>
+      <c r="A11" s="82"/>
+      <c r="B11" s="85"/>
       <c r="C11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="67"/>
-      <c r="E11" s="84"/>
-      <c r="F11" s="87"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="89"/>
+      <c r="F11" s="92"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="61"/>
-      <c r="B12" s="67"/>
+      <c r="A12" s="82"/>
+      <c r="B12" s="85"/>
       <c r="C12" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="67"/>
-      <c r="E12" s="84"/>
-      <c r="F12" s="87"/>
+      <c r="D12" s="85"/>
+      <c r="E12" s="89"/>
+      <c r="F12" s="92"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="61"/>
-      <c r="B13" s="67"/>
+      <c r="A13" s="82"/>
+      <c r="B13" s="85"/>
       <c r="C13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="67"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="87"/>
+      <c r="D13" s="85"/>
+      <c r="E13" s="89"/>
+      <c r="F13" s="92"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="61"/>
-      <c r="B14" s="67"/>
+      <c r="A14" s="82"/>
+      <c r="B14" s="85"/>
       <c r="C14" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="D14" s="67"/>
-      <c r="E14" s="84"/>
-      <c r="F14" s="87"/>
+      <c r="D14" s="85"/>
+      <c r="E14" s="89"/>
+      <c r="F14" s="92"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="61"/>
-      <c r="B15" s="67"/>
+      <c r="A15" s="82"/>
+      <c r="B15" s="85"/>
       <c r="C15" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="67"/>
-      <c r="E15" s="84"/>
-      <c r="F15" s="87"/>
+      <c r="D15" s="85"/>
+      <c r="E15" s="89"/>
+      <c r="F15" s="92"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="61"/>
-      <c r="B16" s="67"/>
+      <c r="A16" s="82"/>
+      <c r="B16" s="85"/>
       <c r="C16" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="D16" s="67"/>
-      <c r="E16" s="84"/>
-      <c r="F16" s="87"/>
+      <c r="D16" s="85"/>
+      <c r="E16" s="89"/>
+      <c r="F16" s="92"/>
     </row>
     <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="62"/>
-      <c r="B17" s="68"/>
+      <c r="A17" s="83"/>
+      <c r="B17" s="86"/>
       <c r="C17" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="68"/>
-      <c r="E17" s="85"/>
-      <c r="F17" s="88"/>
+      <c r="D17" s="86"/>
+      <c r="E17" s="90"/>
+      <c r="F17" s="93"/>
     </row>
     <row r="18" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="39"/>
-      <c r="B18" s="39"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
+      <c r="A18" s="100"/>
+      <c r="B18" s="100"/>
+      <c r="C18" s="100"/>
+      <c r="D18" s="100"/>
+      <c r="E18" s="100"/>
+      <c r="F18" s="100"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="46">
+      <c r="A19" s="50">
         <v>3</v>
       </c>
-      <c r="B19" s="75" t="s">
+      <c r="B19" s="77" t="s">
         <v>20</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="149" t="s">
-        <v>112</v>
-      </c>
-      <c r="E19" s="55" t="s">
+      <c r="D19" s="65" t="s">
+        <v>111</v>
+      </c>
+      <c r="E19" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="F19" s="82" t="s">
+      <c r="F19" s="75" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="47"/>
-      <c r="B20" s="44"/>
+      <c r="A20" s="51"/>
+      <c r="B20" s="45"/>
       <c r="C20" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="44"/>
-      <c r="E20" s="77"/>
-      <c r="F20" s="58"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="62"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
-      <c r="B21" s="44"/>
+      <c r="A21" s="51"/>
+      <c r="B21" s="45"/>
       <c r="C21" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="44"/>
-      <c r="E21" s="77"/>
-      <c r="F21" s="58"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="62"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="47"/>
-      <c r="B22" s="44"/>
+      <c r="A22" s="51"/>
+      <c r="B22" s="45"/>
       <c r="C22" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="44"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="58"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="62"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="47"/>
-      <c r="B23" s="44"/>
+      <c r="A23" s="51"/>
+      <c r="B23" s="45"/>
       <c r="C23" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="44"/>
-      <c r="E23" s="77"/>
-      <c r="F23" s="58"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="62"/>
     </row>
     <row r="24" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="48"/>
-      <c r="B24" s="45"/>
+      <c r="A24" s="52"/>
+      <c r="B24" s="46"/>
       <c r="C24" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D24" s="45"/>
+      <c r="D24" s="46"/>
       <c r="E24" s="56"/>
-      <c r="F24" s="59"/>
+      <c r="F24" s="63"/>
     </row>
     <row r="25" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="39"/>
-      <c r="B25" s="39"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
+      <c r="A25" s="100"/>
+      <c r="B25" s="100"/>
+      <c r="C25" s="100"/>
+      <c r="D25" s="100"/>
+      <c r="E25" s="100"/>
+      <c r="F25" s="100"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="46">
+      <c r="A26" s="50">
         <v>4</v>
       </c>
-      <c r="B26" s="75" t="s">
+      <c r="B26" s="77" t="s">
         <v>4</v>
       </c>
       <c r="C26" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="76" t="s">
+      <c r="D26" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="E26" s="50" t="s">
+      <c r="E26" s="78" t="s">
         <v>100</v>
       </c>
-      <c r="F26" s="82" t="s">
+      <c r="F26" s="75" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="47"/>
-      <c r="B27" s="44"/>
+      <c r="A27" s="51"/>
+      <c r="B27" s="45"/>
       <c r="C27" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D27" s="44"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="58"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="79"/>
+      <c r="F27" s="62"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="47"/>
-      <c r="B28" s="44"/>
+      <c r="A28" s="51"/>
+      <c r="B28" s="45"/>
       <c r="C28" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D28" s="44"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="58"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="79"/>
+      <c r="F28" s="62"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="47"/>
-      <c r="B29" s="44"/>
+      <c r="A29" s="51"/>
+      <c r="B29" s="45"/>
       <c r="C29" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D29" s="44"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="58"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="79"/>
+      <c r="F29" s="62"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="47"/>
-      <c r="B30" s="44"/>
+      <c r="A30" s="51"/>
+      <c r="B30" s="45"/>
       <c r="C30" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="44"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="58"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="79"/>
+      <c r="F30" s="62"/>
     </row>
     <row r="31" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="48"/>
-      <c r="B31" s="45"/>
+      <c r="A31" s="52"/>
+      <c r="B31" s="46"/>
       <c r="C31" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="D31" s="45"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="59"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="80"/>
+      <c r="F31" s="63"/>
     </row>
     <row r="32" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="39"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
+      <c r="A32" s="100"/>
+      <c r="B32" s="100"/>
+      <c r="C32" s="100"/>
+      <c r="D32" s="100"/>
+      <c r="E32" s="100"/>
+      <c r="F32" s="100"/>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="60">
+      <c r="A33" s="81">
         <v>5</v>
       </c>
-      <c r="B33" s="63" t="s">
+      <c r="B33" s="101" t="s">
         <v>3</v>
       </c>
       <c r="C33" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="152" t="s">
-        <v>111</v>
-      </c>
-      <c r="E33" s="69" t="s">
+      <c r="D33" s="87" t="s">
+        <v>110</v>
+      </c>
+      <c r="E33" s="104" t="s">
         <v>101</v>
       </c>
-      <c r="F33" s="72" t="s">
+      <c r="F33" s="107" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="61"/>
-      <c r="B34" s="64"/>
+      <c r="A34" s="82"/>
+      <c r="B34" s="102"/>
       <c r="C34" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D34" s="67"/>
-      <c r="E34" s="70"/>
-      <c r="F34" s="73"/>
+      <c r="D34" s="85"/>
+      <c r="E34" s="105"/>
+      <c r="F34" s="108"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="61"/>
-      <c r="B35" s="64"/>
+      <c r="A35" s="82"/>
+      <c r="B35" s="102"/>
       <c r="C35" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D35" s="67"/>
-      <c r="E35" s="70"/>
-      <c r="F35" s="73"/>
+      <c r="D35" s="85"/>
+      <c r="E35" s="105"/>
+      <c r="F35" s="108"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="61"/>
-      <c r="B36" s="64"/>
+      <c r="A36" s="82"/>
+      <c r="B36" s="102"/>
       <c r="C36" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="67"/>
-      <c r="E36" s="70"/>
-      <c r="F36" s="73"/>
+      <c r="D36" s="85"/>
+      <c r="E36" s="105"/>
+      <c r="F36" s="108"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="61"/>
-      <c r="B37" s="64"/>
+      <c r="A37" s="82"/>
+      <c r="B37" s="102"/>
       <c r="C37" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D37" s="67"/>
-      <c r="E37" s="70"/>
-      <c r="F37" s="73"/>
+      <c r="D37" s="85"/>
+      <c r="E37" s="105"/>
+      <c r="F37" s="108"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="61"/>
-      <c r="B38" s="64"/>
+      <c r="A38" s="82"/>
+      <c r="B38" s="102"/>
       <c r="C38" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D38" s="67"/>
-      <c r="E38" s="70"/>
-      <c r="F38" s="73"/>
+      <c r="D38" s="85"/>
+      <c r="E38" s="105"/>
+      <c r="F38" s="108"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="61"/>
-      <c r="B39" s="64"/>
+      <c r="A39" s="82"/>
+      <c r="B39" s="102"/>
       <c r="C39" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D39" s="67"/>
-      <c r="E39" s="70"/>
-      <c r="F39" s="73"/>
+      <c r="D39" s="85"/>
+      <c r="E39" s="105"/>
+      <c r="F39" s="108"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="61"/>
-      <c r="B40" s="64"/>
+      <c r="A40" s="82"/>
+      <c r="B40" s="102"/>
       <c r="C40" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D40" s="67"/>
-      <c r="E40" s="70"/>
-      <c r="F40" s="73"/>
+      <c r="D40" s="85"/>
+      <c r="E40" s="105"/>
+      <c r="F40" s="108"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="61"/>
-      <c r="B41" s="64"/>
+      <c r="A41" s="82"/>
+      <c r="B41" s="102"/>
       <c r="C41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D41" s="67"/>
-      <c r="E41" s="70"/>
-      <c r="F41" s="73"/>
+      <c r="D41" s="85"/>
+      <c r="E41" s="105"/>
+      <c r="F41" s="108"/>
     </row>
     <row r="42" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="62"/>
-      <c r="B42" s="65"/>
+      <c r="A42" s="83"/>
+      <c r="B42" s="103"/>
       <c r="C42" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D42" s="68"/>
-      <c r="E42" s="71"/>
-      <c r="F42" s="74"/>
+      <c r="D42" s="86"/>
+      <c r="E42" s="106"/>
+      <c r="F42" s="109"/>
     </row>
     <row r="43" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="39"/>
-      <c r="B43" s="39"/>
-      <c r="C43" s="39"/>
-      <c r="D43" s="39"/>
-      <c r="E43" s="39"/>
-      <c r="F43" s="39"/>
+      <c r="A43" s="100"/>
+      <c r="B43" s="100"/>
+      <c r="C43" s="100"/>
+      <c r="D43" s="100"/>
+      <c r="E43" s="100"/>
+      <c r="F43" s="100"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="46">
+      <c r="A44" s="50">
         <v>6</v>
       </c>
-      <c r="B44" s="75" t="s">
+      <c r="B44" s="77" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="D44" s="76" t="s">
+      <c r="D44" s="72" t="s">
         <v>43</v>
       </c>
-      <c r="E44" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="F44" s="57" t="s">
+      <c r="E44" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="F44" s="61" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="47"/>
-      <c r="B45" s="44"/>
+      <c r="A45" s="51"/>
+      <c r="B45" s="45"/>
       <c r="C45" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D45" s="44"/>
-      <c r="E45" s="77"/>
-      <c r="F45" s="58"/>
+      <c r="D45" s="45"/>
+      <c r="E45" s="79"/>
+      <c r="F45" s="62"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="47"/>
-      <c r="B46" s="44"/>
+      <c r="A46" s="51"/>
+      <c r="B46" s="45"/>
       <c r="C46" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D46" s="44"/>
-      <c r="E46" s="77"/>
-      <c r="F46" s="58"/>
+      <c r="D46" s="45"/>
+      <c r="E46" s="79"/>
+      <c r="F46" s="62"/>
     </row>
     <row r="47" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="48"/>
-      <c r="B47" s="45"/>
+      <c r="A47" s="52"/>
+      <c r="B47" s="46"/>
       <c r="C47" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="D47" s="45"/>
-      <c r="E47" s="56"/>
-      <c r="F47" s="59"/>
+      <c r="D47" s="46"/>
+      <c r="E47" s="79"/>
+      <c r="F47" s="63"/>
     </row>
     <row r="48" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="39"/>
-      <c r="B48" s="39"/>
-      <c r="C48" s="39"/>
-      <c r="D48" s="39"/>
-      <c r="E48" s="39"/>
-      <c r="F48" s="39"/>
+      <c r="A48" s="100"/>
+      <c r="B48" s="100"/>
+      <c r="C48" s="100"/>
+      <c r="D48" s="100"/>
+      <c r="E48" s="100"/>
+      <c r="F48" s="100"/>
     </row>
     <row r="49" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="46">
+      <c r="A49" s="50">
         <v>7</v>
       </c>
-      <c r="B49" s="149" t="s">
-        <v>105</v>
-      </c>
-      <c r="C49" s="153" t="s">
+      <c r="B49" s="65" t="s">
+        <v>104</v>
+      </c>
+      <c r="C49" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="D49" s="65" t="s">
         <v>113</v>
       </c>
-      <c r="D49" s="149" t="s">
-        <v>114</v>
-      </c>
-      <c r="E49" s="50" t="s">
+      <c r="E49" s="78" t="s">
         <v>100</v>
       </c>
-      <c r="F49" s="81" t="s">
+      <c r="F49" s="96" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="47"/>
-      <c r="B50" s="78"/>
+      <c r="A50" s="51"/>
+      <c r="B50" s="94"/>
       <c r="C50" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D50" s="44"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="41"/>
+      <c r="D50" s="45"/>
+      <c r="E50" s="79"/>
+      <c r="F50" s="97"/>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="47"/>
-      <c r="B51" s="78"/>
+      <c r="A51" s="51"/>
+      <c r="B51" s="94"/>
       <c r="C51" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D51" s="44"/>
-      <c r="E51" s="51"/>
-      <c r="F51" s="41"/>
+      <c r="D51" s="45"/>
+      <c r="E51" s="79"/>
+      <c r="F51" s="97"/>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="47"/>
-      <c r="B52" s="78"/>
+      <c r="A52" s="51"/>
+      <c r="B52" s="94"/>
       <c r="C52" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D52" s="44"/>
-      <c r="E52" s="51"/>
-      <c r="F52" s="41"/>
+      <c r="D52" s="45"/>
+      <c r="E52" s="79"/>
+      <c r="F52" s="97"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="47"/>
-      <c r="B53" s="78"/>
+      <c r="A53" s="51"/>
+      <c r="B53" s="94"/>
       <c r="C53" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="D53" s="44"/>
-      <c r="E53" s="51"/>
-      <c r="F53" s="41"/>
+      <c r="D53" s="45"/>
+      <c r="E53" s="79"/>
+      <c r="F53" s="97"/>
       <c r="I53" s="6"/>
     </row>
     <row r="54" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="48"/>
-      <c r="B54" s="79"/>
+      <c r="A54" s="52"/>
+      <c r="B54" s="95"/>
       <c r="C54" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="D54" s="45"/>
-      <c r="E54" s="52"/>
-      <c r="F54" s="42"/>
+      <c r="D54" s="46"/>
+      <c r="E54" s="80"/>
+      <c r="F54" s="98"/>
     </row>
     <row r="55" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="39"/>
-      <c r="B55" s="39"/>
-      <c r="C55" s="39"/>
-      <c r="D55" s="39"/>
-      <c r="E55" s="39"/>
-      <c r="F55" s="39"/>
+      <c r="A55" s="100"/>
+      <c r="B55" s="100"/>
+      <c r="C55" s="100"/>
+      <c r="D55" s="100"/>
+      <c r="E55" s="100"/>
+      <c r="F55" s="100"/>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="46">
+      <c r="A56" s="50">
         <v>8</v>
       </c>
-      <c r="B56" s="98" t="s">
+      <c r="B56" s="47" t="s">
         <v>51</v>
       </c>
       <c r="C56" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="D56" s="80" t="s">
+      <c r="D56" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="E56" s="94" t="s">
+      <c r="E56" s="66" t="s">
         <v>103</v>
       </c>
-      <c r="F56" s="97" t="s">
+      <c r="F56" s="68" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="47"/>
-      <c r="B57" s="99"/>
-      <c r="C57" s="154" t="s">
-        <v>115</v>
-      </c>
-      <c r="D57" s="44"/>
-      <c r="E57" s="95"/>
-      <c r="F57" s="58"/>
+      <c r="A57" s="51"/>
+      <c r="B57" s="48"/>
+      <c r="C57" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="D57" s="45"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="62"/>
     </row>
     <row r="58" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="48"/>
-      <c r="B58" s="100"/>
+      <c r="A58" s="52"/>
+      <c r="B58" s="49"/>
       <c r="C58" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="D58" s="45"/>
-      <c r="E58" s="96"/>
-      <c r="F58" s="59"/>
+      <c r="D58" s="46"/>
+      <c r="E58" s="67"/>
+      <c r="F58" s="63"/>
     </row>
     <row r="59" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="39"/>
-      <c r="B59" s="39"/>
-      <c r="C59" s="39"/>
-      <c r="D59" s="39"/>
-      <c r="E59" s="39"/>
-      <c r="F59" s="39"/>
+      <c r="A59" s="100"/>
+      <c r="B59" s="100"/>
+      <c r="C59" s="100"/>
+      <c r="D59" s="100"/>
+      <c r="E59" s="100"/>
+      <c r="F59" s="100"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="46">
+      <c r="A60" s="50">
         <v>9</v>
       </c>
-      <c r="B60" s="49" t="s">
+      <c r="B60" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="C60" s="153" t="s">
+      <c r="C60" s="42" t="s">
+        <v>115</v>
+      </c>
+      <c r="D60" s="65" t="s">
         <v>116</v>
       </c>
-      <c r="D60" s="149" t="s">
-        <v>117</v>
-      </c>
-      <c r="E60" s="94" t="s">
+      <c r="E60" s="66" t="s">
         <v>103</v>
       </c>
-      <c r="F60" s="97" t="s">
+      <c r="F60" s="68" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="48"/>
-      <c r="B61" s="100"/>
+      <c r="A61" s="52"/>
+      <c r="B61" s="49"/>
       <c r="C61" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="D61" s="45"/>
-      <c r="E61" s="96"/>
-      <c r="F61" s="59"/>
+      <c r="D61" s="46"/>
+      <c r="E61" s="67"/>
+      <c r="F61" s="63"/>
     </row>
     <row r="62" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="39"/>
-      <c r="B62" s="39"/>
-      <c r="C62" s="39"/>
-      <c r="D62" s="39"/>
-      <c r="E62" s="39"/>
-      <c r="F62" s="39"/>
+      <c r="A62" s="100"/>
+      <c r="B62" s="100"/>
+      <c r="C62" s="100"/>
+      <c r="D62" s="100"/>
+      <c r="E62" s="100"/>
+      <c r="F62" s="100"/>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="46">
+      <c r="A63" s="50">
         <v>10</v>
       </c>
-      <c r="B63" s="98" t="s">
+      <c r="B63" s="47" t="s">
         <v>58</v>
       </c>
       <c r="C63" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="D63" s="80" t="s">
+      <c r="D63" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="E63" s="55" t="s">
+      <c r="E63" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="F63" s="57" t="s">
+      <c r="F63" s="61" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="47"/>
-      <c r="B64" s="99"/>
+      <c r="A64" s="51"/>
+      <c r="B64" s="48"/>
       <c r="C64" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D64" s="44"/>
-      <c r="E64" s="77"/>
-      <c r="F64" s="58"/>
+      <c r="D64" s="45"/>
+      <c r="E64" s="55"/>
+      <c r="F64" s="62"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="47"/>
-      <c r="B65" s="99"/>
+      <c r="A65" s="51"/>
+      <c r="B65" s="48"/>
       <c r="C65" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D65" s="44"/>
-      <c r="E65" s="77"/>
-      <c r="F65" s="58"/>
+      <c r="D65" s="45"/>
+      <c r="E65" s="55"/>
+      <c r="F65" s="62"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="47"/>
-      <c r="B66" s="99"/>
+      <c r="A66" s="51"/>
+      <c r="B66" s="48"/>
       <c r="C66" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D66" s="44"/>
-      <c r="E66" s="77"/>
-      <c r="F66" s="58"/>
+      <c r="D66" s="45"/>
+      <c r="E66" s="55"/>
+      <c r="F66" s="62"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="47"/>
-      <c r="B67" s="99"/>
+      <c r="A67" s="51"/>
+      <c r="B67" s="48"/>
       <c r="C67" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D67" s="44"/>
-      <c r="E67" s="77"/>
-      <c r="F67" s="58"/>
+      <c r="D67" s="45"/>
+      <c r="E67" s="55"/>
+      <c r="F67" s="62"/>
     </row>
     <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="48"/>
-      <c r="B68" s="100"/>
+      <c r="A68" s="52"/>
+      <c r="B68" s="49"/>
       <c r="C68" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="D68" s="45"/>
+      <c r="D68" s="46"/>
       <c r="E68" s="56"/>
-      <c r="F68" s="59"/>
+      <c r="F68" s="63"/>
     </row>
     <row r="69" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="39"/>
-      <c r="B69" s="39"/>
-      <c r="C69" s="39"/>
-      <c r="D69" s="39"/>
-      <c r="E69" s="39"/>
-      <c r="F69" s="39"/>
+      <c r="A69" s="100"/>
+      <c r="B69" s="100"/>
+      <c r="C69" s="100"/>
+      <c r="D69" s="100"/>
+      <c r="E69" s="100"/>
+      <c r="F69" s="100"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="102">
+      <c r="A70" s="57">
         <v>11</v>
       </c>
-      <c r="B70" s="43" t="s">
+      <c r="B70" s="60" t="s">
         <v>68</v>
       </c>
       <c r="C70" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="D70" s="101" t="s">
+      <c r="D70" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="E70" s="55" t="s">
+      <c r="E70" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="F70" s="57" t="s">
+      <c r="F70" s="61" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="103"/>
-      <c r="B71" s="44"/>
+      <c r="A71" s="58"/>
+      <c r="B71" s="45"/>
       <c r="C71" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D71" s="44"/>
-      <c r="E71" s="77"/>
-      <c r="F71" s="58"/>
+      <c r="D71" s="45"/>
+      <c r="E71" s="55"/>
+      <c r="F71" s="62"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="103"/>
-      <c r="B72" s="44"/>
+      <c r="A72" s="58"/>
+      <c r="B72" s="45"/>
       <c r="C72" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D72" s="44"/>
-      <c r="E72" s="77"/>
-      <c r="F72" s="58"/>
+      <c r="D72" s="45"/>
+      <c r="E72" s="55"/>
+      <c r="F72" s="62"/>
     </row>
     <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="104"/>
-      <c r="B73" s="45"/>
+      <c r="A73" s="59"/>
+      <c r="B73" s="46"/>
       <c r="C73" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="D73" s="45"/>
+      <c r="D73" s="46"/>
       <c r="E73" s="56"/>
-      <c r="F73" s="59"/>
+      <c r="F73" s="63"/>
     </row>
     <row r="74" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="39"/>
-      <c r="B74" s="39"/>
-      <c r="C74" s="39"/>
-      <c r="D74" s="39"/>
-      <c r="E74" s="39"/>
-      <c r="F74" s="39"/>
+      <c r="A74" s="100"/>
+      <c r="B74" s="100"/>
+      <c r="C74" s="100"/>
+      <c r="D74" s="100"/>
+      <c r="E74" s="100"/>
+      <c r="F74" s="100"/>
     </row>
     <row r="75" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="46">
+      <c r="A75" s="50">
         <v>12</v>
       </c>
-      <c r="B75" s="49" t="s">
+      <c r="B75" s="64" t="s">
         <v>70</v>
       </c>
       <c r="C75" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D75" s="53" t="s">
+      <c r="D75" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="E75" s="55" t="s">
-        <v>104</v>
-      </c>
-      <c r="F75" s="40" t="s">
+      <c r="E75" s="66" t="s">
+        <v>103</v>
+      </c>
+      <c r="F75" s="99" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="48"/>
-      <c r="B76" s="45"/>
+      <c r="A76" s="52"/>
+      <c r="B76" s="46"/>
       <c r="C76" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="D76" s="54"/>
-      <c r="E76" s="56"/>
-      <c r="F76" s="42"/>
+      <c r="D76" s="111"/>
+      <c r="E76" s="67"/>
+      <c r="F76" s="98"/>
     </row>
     <row r="77" spans="1:6" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="39"/>
-      <c r="B77" s="39"/>
-      <c r="C77" s="39"/>
-      <c r="D77" s="39"/>
-      <c r="E77" s="39"/>
-      <c r="F77" s="39"/>
+      <c r="A77" s="100"/>
+      <c r="B77" s="100"/>
+      <c r="C77" s="100"/>
+      <c r="D77" s="100"/>
+      <c r="E77" s="100"/>
+      <c r="F77" s="100"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="46">
+      <c r="A78" s="50">
         <v>13</v>
       </c>
-      <c r="B78" s="49" t="s">
+      <c r="B78" s="64" t="s">
         <v>89</v>
       </c>
       <c r="C78" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="D78" s="43" t="s">
+      <c r="D78" s="60" t="s">
         <v>80</v>
       </c>
-      <c r="E78" s="50" t="s">
+      <c r="E78" s="78" t="s">
         <v>100</v>
       </c>
-      <c r="F78" s="40" t="s">
+      <c r="F78" s="99" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="47"/>
-      <c r="B79" s="44"/>
+      <c r="A79" s="51"/>
+      <c r="B79" s="45"/>
       <c r="C79" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D79" s="44"/>
-      <c r="E79" s="51"/>
-      <c r="F79" s="41"/>
+      <c r="D79" s="45"/>
+      <c r="E79" s="79"/>
+      <c r="F79" s="97"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="47"/>
-      <c r="B80" s="44"/>
+      <c r="A80" s="51"/>
+      <c r="B80" s="45"/>
       <c r="C80" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D80" s="44"/>
-      <c r="E80" s="51"/>
-      <c r="F80" s="41"/>
+      <c r="D80" s="45"/>
+      <c r="E80" s="79"/>
+      <c r="F80" s="97"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="47"/>
-      <c r="B81" s="44"/>
-      <c r="C81" s="154" t="s">
+      <c r="A81" s="51"/>
+      <c r="B81" s="45"/>
+      <c r="C81" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="D81" s="44"/>
-      <c r="E81" s="51"/>
-      <c r="F81" s="41"/>
+      <c r="D81" s="45"/>
+      <c r="E81" s="79"/>
+      <c r="F81" s="97"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="47"/>
-      <c r="B82" s="44"/>
+      <c r="A82" s="51"/>
+      <c r="B82" s="45"/>
       <c r="C82" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D82" s="44"/>
-      <c r="E82" s="51"/>
-      <c r="F82" s="41"/>
+      <c r="D82" s="45"/>
+      <c r="E82" s="79"/>
+      <c r="F82" s="97"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="47"/>
-      <c r="B83" s="44"/>
+      <c r="A83" s="51"/>
+      <c r="B83" s="45"/>
       <c r="C83" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D83" s="44"/>
-      <c r="E83" s="51"/>
-      <c r="F83" s="41"/>
+      <c r="D83" s="45"/>
+      <c r="E83" s="79"/>
+      <c r="F83" s="97"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="47"/>
-      <c r="B84" s="44"/>
+      <c r="A84" s="51"/>
+      <c r="B84" s="45"/>
       <c r="C84" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D84" s="44"/>
-      <c r="E84" s="51"/>
-      <c r="F84" s="41"/>
+      <c r="D84" s="45"/>
+      <c r="E84" s="79"/>
+      <c r="F84" s="97"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="47"/>
-      <c r="B85" s="44"/>
-      <c r="C85" s="154" t="s">
-        <v>118</v>
-      </c>
-      <c r="D85" s="44"/>
-      <c r="E85" s="51"/>
-      <c r="F85" s="41"/>
+      <c r="A85" s="51"/>
+      <c r="B85" s="45"/>
+      <c r="C85" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="D85" s="45"/>
+      <c r="E85" s="79"/>
+      <c r="F85" s="97"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="47"/>
-      <c r="B86" s="44"/>
+      <c r="A86" s="51"/>
+      <c r="B86" s="45"/>
       <c r="C86" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D86" s="44"/>
-      <c r="E86" s="51"/>
-      <c r="F86" s="41"/>
+      <c r="D86" s="45"/>
+      <c r="E86" s="79"/>
+      <c r="F86" s="97"/>
     </row>
     <row r="87" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="48"/>
-      <c r="B87" s="45"/>
+      <c r="A87" s="52"/>
+      <c r="B87" s="46"/>
       <c r="C87" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D87" s="45"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="42"/>
+      <c r="D87" s="46"/>
+      <c r="E87" s="80"/>
+      <c r="F87" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="D70:D73"/>
-    <mergeCell ref="B63:B68"/>
-    <mergeCell ref="A63:A68"/>
-    <mergeCell ref="D63:D68"/>
-    <mergeCell ref="E63:E68"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="B70:B73"/>
-    <mergeCell ref="E70:E73"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="F63:F68"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="D60:D61"/>
-    <mergeCell ref="E60:E61"/>
-    <mergeCell ref="F60:F61"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="D3:D6"/>
-    <mergeCell ref="E3:E6"/>
-    <mergeCell ref="F3:F6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A19:A24"/>
-    <mergeCell ref="B19:B24"/>
-    <mergeCell ref="D19:D24"/>
-    <mergeCell ref="E19:E24"/>
-    <mergeCell ref="F19:F24"/>
-    <mergeCell ref="B26:B31"/>
-    <mergeCell ref="D26:D31"/>
-    <mergeCell ref="E26:E31"/>
-    <mergeCell ref="F26:F31"/>
-    <mergeCell ref="A8:A17"/>
-    <mergeCell ref="B8:B17"/>
-    <mergeCell ref="D8:D17"/>
-    <mergeCell ref="E8:E17"/>
-    <mergeCell ref="F8:F17"/>
-    <mergeCell ref="B49:B54"/>
-    <mergeCell ref="A49:A54"/>
-    <mergeCell ref="D49:D54"/>
-    <mergeCell ref="E49:E54"/>
-    <mergeCell ref="F49:F54"/>
-    <mergeCell ref="F78:F87"/>
-    <mergeCell ref="D78:D87"/>
-    <mergeCell ref="A78:A87"/>
-    <mergeCell ref="B78:B87"/>
-    <mergeCell ref="E78:E87"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A33:A42"/>
-    <mergeCell ref="B33:B42"/>
-    <mergeCell ref="D33:D42"/>
-    <mergeCell ref="E33:E42"/>
-    <mergeCell ref="F33:F42"/>
-    <mergeCell ref="A44:A47"/>
-    <mergeCell ref="B44:B47"/>
-    <mergeCell ref="D44:D47"/>
-    <mergeCell ref="E44:E47"/>
-    <mergeCell ref="F44:F47"/>
-    <mergeCell ref="A26:A31"/>
     <mergeCell ref="A77:F77"/>
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="A59:F59"/>
@@ -2984,6 +2922,68 @@
     <mergeCell ref="E56:E58"/>
     <mergeCell ref="F56:F58"/>
     <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A33:A42"/>
+    <mergeCell ref="B33:B42"/>
+    <mergeCell ref="D33:D42"/>
+    <mergeCell ref="E33:E42"/>
+    <mergeCell ref="F33:F42"/>
+    <mergeCell ref="A44:A47"/>
+    <mergeCell ref="B44:B47"/>
+    <mergeCell ref="D44:D47"/>
+    <mergeCell ref="E44:E47"/>
+    <mergeCell ref="F44:F47"/>
+    <mergeCell ref="F78:F87"/>
+    <mergeCell ref="D78:D87"/>
+    <mergeCell ref="A78:A87"/>
+    <mergeCell ref="B78:B87"/>
+    <mergeCell ref="E78:E87"/>
+    <mergeCell ref="B49:B54"/>
+    <mergeCell ref="A49:A54"/>
+    <mergeCell ref="D49:D54"/>
+    <mergeCell ref="E49:E54"/>
+    <mergeCell ref="F49:F54"/>
+    <mergeCell ref="B26:B31"/>
+    <mergeCell ref="D26:D31"/>
+    <mergeCell ref="E26:E31"/>
+    <mergeCell ref="F26:F31"/>
+    <mergeCell ref="A8:A17"/>
+    <mergeCell ref="B8:B17"/>
+    <mergeCell ref="D8:D17"/>
+    <mergeCell ref="E8:E17"/>
+    <mergeCell ref="F8:F17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A26:A31"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A19:A24"/>
+    <mergeCell ref="B19:B24"/>
+    <mergeCell ref="D19:D24"/>
+    <mergeCell ref="E19:E24"/>
+    <mergeCell ref="F19:F24"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="E3:E6"/>
+    <mergeCell ref="F3:F6"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="F63:F68"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="D60:D61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="D70:D73"/>
+    <mergeCell ref="B63:B68"/>
+    <mergeCell ref="A63:A68"/>
+    <mergeCell ref="D63:D68"/>
+    <mergeCell ref="E63:E68"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="B70:B73"/>
+    <mergeCell ref="E70:E73"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3009,16 +3009,16 @@
       <c r="A1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="130" t="s">
-        <v>106</v>
-      </c>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="132"/>
+      <c r="B1" s="113" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="115"/>
     </row>
     <row r="2" spans="1:9" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
@@ -3050,293 +3050,288 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="133">
+      <c r="A3" s="116">
         <v>1</v>
       </c>
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="119" t="s">
         <v>99</v>
       </c>
       <c r="C3" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="119" t="s">
         <v>119</v>
       </c>
-      <c r="D3" s="105" t="s">
+      <c r="E3" s="119" t="s">
         <v>120</v>
       </c>
-      <c r="E3" s="105" t="s">
-        <v>121</v>
-      </c>
-      <c r="F3" s="118" t="s">
+      <c r="F3" s="122" t="s">
         <v>94</v>
       </c>
-      <c r="G3" s="140" t="s">
+      <c r="G3" s="125" t="s">
         <v>95</v>
       </c>
-      <c r="H3" s="115" t="s">
+      <c r="H3" s="133" t="s">
         <v>100</v>
       </c>
-      <c r="I3" s="143" t="s">
+      <c r="I3" s="128" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="134"/>
-      <c r="B4" s="136"/>
+      <c r="A4" s="117"/>
+      <c r="B4" s="120"/>
       <c r="C4" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="136"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="141"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="144"/>
+      <c r="D4" s="120"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="123"/>
+      <c r="G4" s="126"/>
+      <c r="H4" s="134"/>
+      <c r="I4" s="129"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="134"/>
-      <c r="B5" s="136"/>
+      <c r="A5" s="117"/>
+      <c r="B5" s="120"/>
       <c r="C5" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="136"/>
-      <c r="E5" s="136"/>
-      <c r="F5" s="138"/>
-      <c r="G5" s="141"/>
-      <c r="H5" s="116"/>
-      <c r="I5" s="144"/>
+      <c r="D5" s="120"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="123"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="129"/>
     </row>
     <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="135"/>
-      <c r="B6" s="137"/>
+      <c r="A6" s="118"/>
+      <c r="B6" s="121"/>
       <c r="C6" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="137"/>
-      <c r="E6" s="137"/>
-      <c r="F6" s="139"/>
-      <c r="G6" s="142"/>
-      <c r="H6" s="117"/>
-      <c r="I6" s="145"/>
+      <c r="D6" s="121"/>
+      <c r="E6" s="121"/>
+      <c r="F6" s="124"/>
+      <c r="G6" s="127"/>
+      <c r="H6" s="135"/>
+      <c r="I6" s="130"/>
     </row>
     <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="146"/>
-      <c r="B7" s="146"/>
-      <c r="C7" s="146"/>
-      <c r="D7" s="146"/>
-      <c r="E7" s="146"/>
-      <c r="F7" s="146"/>
-      <c r="G7" s="146"/>
-      <c r="H7" s="146"/>
-      <c r="I7" s="146"/>
+      <c r="A7" s="145"/>
+      <c r="B7" s="145"/>
+      <c r="C7" s="145"/>
+      <c r="D7" s="145"/>
+      <c r="E7" s="145"/>
+      <c r="F7" s="145"/>
+      <c r="G7" s="145"/>
+      <c r="H7" s="145"/>
+      <c r="I7" s="145"/>
     </row>
     <row r="8" spans="1:9" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="108">
+      <c r="A8" s="148">
         <v>2</v>
       </c>
-      <c r="B8" s="110" t="s">
-        <v>122</v>
+      <c r="B8" s="150" t="s">
+        <v>121</v>
       </c>
       <c r="C8" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="D8" s="105" t="s">
+      <c r="D8" s="119" t="s">
         <v>97</v>
       </c>
-      <c r="E8" s="105" t="s">
-        <v>123</v>
-      </c>
-      <c r="F8" s="118" t="s">
+      <c r="E8" s="119" t="s">
+        <v>122</v>
+      </c>
+      <c r="F8" s="122" t="s">
         <v>94</v>
       </c>
-      <c r="G8" s="121" t="s">
+      <c r="G8" s="138" t="s">
         <v>95</v>
       </c>
-      <c r="H8" s="128" t="s">
-        <v>101</v>
-      </c>
-      <c r="I8" s="113" t="s">
+      <c r="H8" s="66" t="s">
+        <v>103</v>
+      </c>
+      <c r="I8" s="131" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="109"/>
-      <c r="B9" s="111"/>
+      <c r="A9" s="149"/>
+      <c r="B9" s="151"/>
       <c r="C9" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="107"/>
-      <c r="E9" s="107"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="123"/>
-      <c r="H9" s="129"/>
-      <c r="I9" s="114"/>
+      <c r="D9" s="147"/>
+      <c r="E9" s="147"/>
+      <c r="F9" s="137"/>
+      <c r="G9" s="140"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="132"/>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="146"/>
-      <c r="B10" s="146"/>
-      <c r="C10" s="146"/>
-      <c r="D10" s="146"/>
-      <c r="E10" s="146"/>
-      <c r="F10" s="146"/>
-      <c r="G10" s="146"/>
-      <c r="H10" s="146"/>
-      <c r="I10" s="146"/>
+      <c r="A10" s="145"/>
+      <c r="B10" s="145"/>
+      <c r="C10" s="145"/>
+      <c r="D10" s="145"/>
+      <c r="E10" s="145"/>
+      <c r="F10" s="145"/>
+      <c r="G10" s="145"/>
+      <c r="H10" s="145"/>
+      <c r="I10" s="145"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="108">
+      <c r="A11" s="148">
         <v>3</v>
       </c>
-      <c r="B11" s="105" t="s">
+      <c r="B11" s="119" t="s">
         <v>102</v>
       </c>
       <c r="C11" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="105" t="s">
-        <v>124</v>
-      </c>
-      <c r="E11" s="105" t="s">
+      <c r="D11" s="119" t="s">
+        <v>123</v>
+      </c>
+      <c r="E11" s="119" t="s">
         <v>98</v>
       </c>
-      <c r="F11" s="118" t="s">
+      <c r="F11" s="122" t="s">
         <v>94</v>
       </c>
-      <c r="G11" s="121" t="s">
+      <c r="G11" s="138" t="s">
         <v>95</v>
       </c>
-      <c r="H11" s="124" t="s">
+      <c r="H11" s="141" t="s">
         <v>100</v>
       </c>
-      <c r="I11" s="113" t="s">
+      <c r="I11" s="131" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="112"/>
-      <c r="B12" s="106"/>
+      <c r="A12" s="152"/>
+      <c r="B12" s="146"/>
       <c r="C12" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="106"/>
-      <c r="E12" s="106"/>
-      <c r="F12" s="119"/>
-      <c r="G12" s="122"/>
-      <c r="H12" s="125"/>
-      <c r="I12" s="127"/>
+      <c r="D12" s="146"/>
+      <c r="E12" s="146"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="139"/>
+      <c r="H12" s="142"/>
+      <c r="I12" s="144"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="112"/>
-      <c r="B13" s="106"/>
+      <c r="A13" s="152"/>
+      <c r="B13" s="146"/>
       <c r="C13" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="D13" s="106"/>
-      <c r="E13" s="106"/>
-      <c r="F13" s="119"/>
-      <c r="G13" s="122"/>
-      <c r="H13" s="125"/>
-      <c r="I13" s="127"/>
+      <c r="D13" s="146"/>
+      <c r="E13" s="146"/>
+      <c r="F13" s="136"/>
+      <c r="G13" s="139"/>
+      <c r="H13" s="142"/>
+      <c r="I13" s="144"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="112"/>
-      <c r="B14" s="106"/>
+      <c r="A14" s="152"/>
+      <c r="B14" s="146"/>
       <c r="C14" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D14" s="106"/>
-      <c r="E14" s="106"/>
-      <c r="F14" s="119"/>
-      <c r="G14" s="122"/>
-      <c r="H14" s="125"/>
-      <c r="I14" s="127"/>
+      <c r="D14" s="146"/>
+      <c r="E14" s="146"/>
+      <c r="F14" s="136"/>
+      <c r="G14" s="139"/>
+      <c r="H14" s="142"/>
+      <c r="I14" s="144"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="112"/>
-      <c r="B15" s="106"/>
+      <c r="A15" s="152"/>
+      <c r="B15" s="146"/>
       <c r="C15" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="106"/>
-      <c r="E15" s="106"/>
-      <c r="F15" s="119"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="125"/>
-      <c r="I15" s="127"/>
+      <c r="D15" s="146"/>
+      <c r="E15" s="146"/>
+      <c r="F15" s="136"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="142"/>
+      <c r="I15" s="144"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="112"/>
-      <c r="B16" s="106"/>
+      <c r="A16" s="152"/>
+      <c r="B16" s="146"/>
       <c r="C16" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="106"/>
-      <c r="E16" s="106"/>
-      <c r="F16" s="119"/>
-      <c r="G16" s="122"/>
-      <c r="H16" s="125"/>
-      <c r="I16" s="127"/>
+      <c r="D16" s="146"/>
+      <c r="E16" s="146"/>
+      <c r="F16" s="136"/>
+      <c r="G16" s="139"/>
+      <c r="H16" s="142"/>
+      <c r="I16" s="144"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="112"/>
-      <c r="B17" s="106"/>
+      <c r="A17" s="152"/>
+      <c r="B17" s="146"/>
       <c r="C17" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="106"/>
-      <c r="E17" s="106"/>
-      <c r="F17" s="119"/>
-      <c r="G17" s="122"/>
-      <c r="H17" s="125"/>
-      <c r="I17" s="127"/>
+      <c r="D17" s="146"/>
+      <c r="E17" s="146"/>
+      <c r="F17" s="136"/>
+      <c r="G17" s="139"/>
+      <c r="H17" s="142"/>
+      <c r="I17" s="144"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="112"/>
-      <c r="B18" s="106"/>
+      <c r="A18" s="152"/>
+      <c r="B18" s="146"/>
       <c r="C18" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="D18" s="106"/>
-      <c r="E18" s="106"/>
-      <c r="F18" s="119"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="125"/>
-      <c r="I18" s="127"/>
+      <c r="D18" s="146"/>
+      <c r="E18" s="146"/>
+      <c r="F18" s="136"/>
+      <c r="G18" s="139"/>
+      <c r="H18" s="142"/>
+      <c r="I18" s="144"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="112"/>
-      <c r="B19" s="106"/>
+      <c r="A19" s="152"/>
+      <c r="B19" s="146"/>
       <c r="C19" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="106"/>
-      <c r="E19" s="106"/>
-      <c r="F19" s="119"/>
-      <c r="G19" s="122"/>
-      <c r="H19" s="125"/>
-      <c r="I19" s="127"/>
+      <c r="D19" s="146"/>
+      <c r="E19" s="146"/>
+      <c r="F19" s="136"/>
+      <c r="G19" s="139"/>
+      <c r="H19" s="142"/>
+      <c r="I19" s="144"/>
     </row>
     <row r="20" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="109"/>
-      <c r="B20" s="107"/>
+      <c r="A20" s="149"/>
+      <c r="B20" s="147"/>
       <c r="C20" s="27" t="s">
-        <v>125</v>
-      </c>
-      <c r="D20" s="107"/>
-      <c r="E20" s="107"/>
-      <c r="F20" s="120"/>
-      <c r="G20" s="123"/>
-      <c r="H20" s="126"/>
-      <c r="I20" s="114"/>
+        <v>124</v>
+      </c>
+      <c r="D20" s="147"/>
+      <c r="E20" s="147"/>
+      <c r="F20" s="137"/>
+      <c r="G20" s="140"/>
+      <c r="H20" s="143"/>
+      <c r="I20" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="D3:D6"/>
-    <mergeCell ref="E3:E6"/>
-    <mergeCell ref="F3:F6"/>
-    <mergeCell ref="G3:G6"/>
-    <mergeCell ref="I3:I6"/>
+    <mergeCell ref="D11:D20"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="H3:H6"/>
     <mergeCell ref="F11:F20"/>
@@ -3353,9 +3348,14 @@
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B11:B20"/>
     <mergeCell ref="A11:A20"/>
-    <mergeCell ref="D11:D20"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="E3:E6"/>
+    <mergeCell ref="F3:F6"/>
+    <mergeCell ref="G3:G6"/>
+    <mergeCell ref="I3:I6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G11:G20" r:id="rId1" display="Click" xr:uid="{8820644A-41A1-4803-9FE0-E7A0CF342047}"/>
